--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>12.71762946922157</v>
+        <v>2.066614788748505</v>
       </c>
       <c r="D2" t="n">
-        <v>3.136719997972233</v>
+        <v>0.5097169996704879</v>
       </c>
       <c r="E2" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F2" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.48926732472812</v>
+        <v>1.867005940268319</v>
       </c>
       <c r="D3" t="n">
-        <v>10.63634638436435</v>
+        <v>1.728406287459206</v>
       </c>
       <c r="E3" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F3" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.51576859585917</v>
+        <v>2.358812396827115</v>
       </c>
       <c r="D4" t="n">
-        <v>13.34384577694248</v>
+        <v>2.168374938753153</v>
       </c>
       <c r="E4" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F4" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.92106914299299</v>
+        <v>2.587173735736361</v>
       </c>
       <c r="D5" t="n">
-        <v>6.643744862763365</v>
+        <v>1.079608540199047</v>
       </c>
       <c r="E5" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F5" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.04945508237885</v>
+        <v>0.9830364508865631</v>
       </c>
       <c r="D6" t="n">
-        <v>1.840893502864553</v>
+        <v>0.29914519421549</v>
       </c>
       <c r="E6" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F6" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>8.72824862148415</v>
+        <v>1.418340400991174</v>
       </c>
       <c r="D7" t="n">
-        <v>10.98678077015166</v>
+        <v>1.785351875149645</v>
       </c>
       <c r="E7" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F7" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.63383130124824</v>
+        <v>4.00299758645284</v>
       </c>
       <c r="D8" t="n">
-        <v>19.29548217825539</v>
+        <v>3.135515853966502</v>
       </c>
       <c r="E8" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F8" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.86514818338801</v>
+        <v>2.415586579800551</v>
       </c>
       <c r="D9" t="n">
-        <v>10.55826894519859</v>
+        <v>1.715718703594771</v>
       </c>
       <c r="E9" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F9" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.02209449948767</v>
+        <v>6.991090356166747</v>
       </c>
       <c r="D10" t="n">
-        <v>35.11654083641537</v>
+        <v>5.706437885917498</v>
       </c>
       <c r="E10" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F10" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.22860599185097</v>
+        <v>4.262148473675782</v>
       </c>
       <c r="D11" t="n">
-        <v>27.01557571164952</v>
+        <v>4.390031053143048</v>
       </c>
       <c r="E11" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F11" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.91372185857156</v>
+        <v>3.885979802017879</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61618985046987</v>
+        <v>3.350130850701354</v>
       </c>
       <c r="E12" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F12" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.15107775211695</v>
+        <v>6.849550134719006</v>
       </c>
       <c r="D13" t="n">
-        <v>39.23803540228895</v>
+        <v>6.376180752871955</v>
       </c>
       <c r="E13" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F13" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.28967854943804</v>
+        <v>5.734572764283681</v>
       </c>
       <c r="D14" t="n">
-        <v>33.5764383843557</v>
+        <v>5.456171237457802</v>
       </c>
       <c r="E14" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F14" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>42.8282693625729</v>
+        <v>6.959593771418096</v>
       </c>
       <c r="D15" t="n">
-        <v>43.27282013550336</v>
+        <v>7.031833272019296</v>
       </c>
       <c r="E15" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F15" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>23.84724086064699</v>
+        <v>3.875176639855136</v>
       </c>
       <c r="D16" t="n">
-        <v>23.66270330005044</v>
+        <v>3.845189286258196</v>
       </c>
       <c r="E16" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F16" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>40.95424275945045</v>
+        <v>6.655064448410698</v>
       </c>
       <c r="D17" t="n">
-        <v>41.09661446927816</v>
+        <v>6.678199851257701</v>
       </c>
       <c r="E17" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F17" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>36.25761100113146</v>
+        <v>5.891861787683863</v>
       </c>
       <c r="D18" t="n">
-        <v>36.32895565077259</v>
+        <v>5.903455293250547</v>
       </c>
       <c r="E18" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F18" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.01392980983693</v>
+        <v>5.852263594098502</v>
       </c>
       <c r="D19" t="n">
-        <v>28.61381776158898</v>
+        <v>4.64974538625821</v>
       </c>
       <c r="E19" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F19" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>22.31167250733651</v>
+        <v>3.625646782442183</v>
       </c>
       <c r="D20" t="n">
-        <v>10.18941361013612</v>
+        <v>1.65577971164712</v>
       </c>
       <c r="E20" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F20" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>35.03443684014177</v>
+        <v>5.693095986523037</v>
       </c>
       <c r="D21" t="n">
-        <v>36.94900999870094</v>
+        <v>6.004214124788903</v>
       </c>
       <c r="E21" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F21" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>26.5145338977041</v>
+        <v>4.308611758376917</v>
       </c>
       <c r="D22" t="n">
-        <v>26.20264387868728</v>
+        <v>4.257929630286684</v>
       </c>
       <c r="E22" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F22" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>7.013851931970842</v>
+        <v>1.139750938945262</v>
       </c>
       <c r="D23" t="n">
-        <v>8.445936137492348</v>
+        <v>1.372464622342507</v>
       </c>
       <c r="E23" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F23" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>39.11387518894016</v>
+        <v>6.356004718202777</v>
       </c>
       <c r="D24" t="n">
-        <v>39.14596222468543</v>
+        <v>6.361218861511383</v>
       </c>
       <c r="E24" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F24" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>14.25231577658413</v>
+        <v>2.316001313694922</v>
       </c>
       <c r="D25" t="n">
-        <v>13.3556685930369</v>
+        <v>2.170296146368497</v>
       </c>
       <c r="E25" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F25" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>20.40942592829893</v>
+        <v>3.316531713348576</v>
       </c>
       <c r="D26" t="n">
-        <v>19.41087272375286</v>
+        <v>3.154266817609841</v>
       </c>
       <c r="E26" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F26" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>3.525822733389357</v>
+        <v>0.5729461941757706</v>
       </c>
       <c r="D27" t="n">
-        <v>10.93489053415129</v>
+        <v>1.776919711799584</v>
       </c>
       <c r="E27" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F27" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>7.034578460550928</v>
+        <v>1.143118999839526</v>
       </c>
       <c r="D28" t="n">
-        <v>13.88788488152812</v>
+        <v>2.256781293248319</v>
       </c>
       <c r="E28" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F28" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>11.04442918801406</v>
+        <v>1.794719743052285</v>
       </c>
       <c r="D29" t="n">
-        <v>10.89867142317216</v>
+        <v>1.771034106265477</v>
       </c>
       <c r="E29" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F29" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>3.972422526209678</v>
+        <v>0.6455186605090727</v>
       </c>
       <c r="D30" t="n">
-        <v>4.155967327986975</v>
+        <v>0.6753446907978834</v>
       </c>
       <c r="E30" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F30" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>9.576504957204158</v>
+        <v>1.556182055545676</v>
       </c>
       <c r="D31" t="n">
-        <v>12.19141273668315</v>
+        <v>1.981104569711012</v>
       </c>
       <c r="E31" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F31" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>19.44619429819478</v>
+        <v>3.160006573456652</v>
       </c>
       <c r="D32" t="n">
-        <v>22.04290692609041</v>
+        <v>3.581972375489692</v>
       </c>
       <c r="E32" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F32" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>33.25063148056087</v>
+        <v>5.403227615591142</v>
       </c>
       <c r="D33" t="n">
-        <v>5.211208860461589</v>
+        <v>0.8468214398250082</v>
       </c>
       <c r="E33" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F33" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>30.29904330584844</v>
+        <v>4.923594537200371</v>
       </c>
       <c r="D34" t="n">
-        <v>26.25590908318223</v>
+        <v>4.266585226017113</v>
       </c>
       <c r="E34" t="n">
-        <v>12.49161877838304</v>
+        <v>2.029888051487243</v>
       </c>
       <c r="F34" t="n">
-        <v>12.32297338818586</v>
+        <v>2.002483175580202</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
